--- a/06_manuscript/ijir_v0_3_5_20260728/05_tables/IJIR_Table_2_Forward_Nominal_Associations_v0_3_5.xlsx
+++ b/06_manuscript/ijir_v0_3_5_20260728/05_tables/IJIR_Table_2_Forward_Nominal_Associations_v0_3_5.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table" sheetId="1" r:id="R5173535b4b3a42a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R24a3cd5591a94f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table" sheetId="1" r:id="Rf04680caa7c34364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="Ra4ef9f0ad5af4ba9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -572,7 +572,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d6215fa1ca148ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145afe93e933411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -612,7 +612,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac10fcb366d44760"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c86bcd8a9d84b28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/06_manuscript/ijir_v0_3_5_20260728/05_tables/IJIR_Table_2_Forward_Nominal_Associations_v0_3_5.xlsx
+++ b/06_manuscript/ijir_v0_3_5_20260728/05_tables/IJIR_Table_2_Forward_Nominal_Associations_v0_3_5.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table" sheetId="1" r:id="Rf04680caa7c34364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="Ra4ef9f0ad5af4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table" sheetId="1" r:id="Rd68b5bef6f31476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R17a90301cf464e4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -572,7 +572,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145afe93e933411d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5795cde819ca4cc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -612,7 +612,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c86bcd8a9d84b28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ea1df000144ab2"/>
   </x:tableParts>
 </x:worksheet>
 </file>